--- a/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/claude-haiku-4-5_task4_token_usage.xlsx
+++ b/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/claude-haiku-4-5_task4_token_usage.xlsx
@@ -1,72 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wiamlachqer/Library/Mobile Documents/com~apple~CloudDocs/Capstone/Multi-Agents-Systems-Benchmarking-for-Software-Engineering/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57270BB6-D3FD-AF4A-9D43-DB62B34579F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="token_usage" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="token_usage" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
-  <si>
-    <t>sample_idx</t>
-  </si>
-  <si>
-    <t>agent</t>
-  </si>
-  <si>
-    <t>input_tokens</t>
-  </si>
-  <si>
-    <t>output_tokens</t>
-  </si>
-  <si>
-    <t>total_tokens</t>
-  </si>
-  <si>
-    <t>supervisor</t>
-  </si>
-  <si>
-    <t>code_analyser</t>
-  </si>
-  <si>
-    <t>finalizer</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -81,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -405,98 +420,191 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="21.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>sample_idx</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>input_tokens</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>output_tokens</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>total_tokens</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>554</v>
+      </c>
+      <c r="D2" t="n">
+        <v>720</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D3" t="n">
+        <v>226</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1484</v>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
+      <c r="E4" t="n">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1426</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>554</v>
       </c>
-      <c r="D2">
-        <v>720</v>
-      </c>
-      <c r="E2">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>1221</v>
-      </c>
-      <c r="D3">
-        <v>226</v>
-      </c>
-      <c r="E3">
-        <v>1447</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>1484</v>
-      </c>
-      <c r="D4">
+      <c r="D6" t="n">
+        <v>905</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1459</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1406</v>
+      </c>
+      <c r="D7" t="n">
+        <v>272</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1715</v>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>1487</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>1426</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1429</v>
+      <c r="E8" t="n">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1657</v>
+      </c>
+      <c r="D9" t="n">
+        <v>205</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1862</v>
       </c>
     </row>
   </sheetData>

--- a/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/claude-haiku-4-5_task4_token_usage.xlsx
+++ b/DependEval/results/task4/AtoA/python/claude-haiku-4-5-python/claude-haiku-4-5_task4_token_usage.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>554</v>
+        <v>614</v>
       </c>
       <c r="D2" t="n">
-        <v>720</v>
+        <v>98</v>
       </c>
       <c r="E2" t="n">
-        <v>1274</v>
+        <v>712</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1221</v>
+        <v>631</v>
       </c>
       <c r="D3" t="n">
-        <v>226</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
-        <v>1447</v>
+        <v>734</v>
       </c>
     </row>
     <row r="4">
@@ -499,17 +499,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>supervisor</t>
+          <t>critic</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1484</v>
+        <v>616</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>330</v>
       </c>
       <c r="E4" t="n">
-        <v>1487</v>
+        <v>946</v>
       </c>
     </row>
     <row r="5">
@@ -518,17 +518,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>finalizer</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1426</v>
+        <v>998</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="E5" t="n">
-        <v>1429</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="6">
@@ -537,17 +537,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>supervisor</t>
+          <t>code_analyser</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>554</v>
+        <v>988</v>
       </c>
       <c r="D6" t="n">
-        <v>905</v>
+        <v>85</v>
       </c>
       <c r="E6" t="n">
-        <v>1459</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="7">
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>code_analyser</t>
+          <t>supervisor</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1406</v>
+        <v>1096</v>
       </c>
       <c r="D7" t="n">
-        <v>272</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1678</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="8">
@@ -575,17 +575,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>supervisor</t>
+          <t>finalizer</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1715</v>
+        <v>980</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>130</v>
       </c>
       <c r="E8" t="n">
-        <v>1718</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="9">
@@ -594,17 +594,6800 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>614</v>
+      </c>
+      <c r="D9" t="n">
+        <v>98</v>
+      </c>
+      <c r="E9" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>631</v>
+      </c>
+      <c r="D10" t="n">
+        <v>103</v>
+      </c>
+      <c r="E10" t="n">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>616</v>
+      </c>
+      <c r="D11" t="n">
+        <v>308</v>
+      </c>
+      <c r="E11" t="n">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>976</v>
+      </c>
+      <c r="D12" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>977</v>
+      </c>
+      <c r="D13" t="n">
+        <v>85</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1085</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>finalizer</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>1657</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C15" t="n">
+        <v>969</v>
+      </c>
+      <c r="D15" t="n">
+        <v>162</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>848</v>
+      </c>
+      <c r="D16" t="n">
+        <v>75</v>
+      </c>
+      <c r="E16" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>842</v>
+      </c>
+      <c r="D17" t="n">
+        <v>189</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>913</v>
+      </c>
+      <c r="D18" t="n">
+        <v>391</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1356</v>
+      </c>
+      <c r="D19" t="n">
+        <v>49</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1342</v>
+      </c>
+      <c r="D20" t="n">
+        <v>174</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1539</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1423</v>
+      </c>
+      <c r="D22" t="n">
+        <v>282</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>607</v>
+      </c>
+      <c r="D23" t="n">
+        <v>69</v>
+      </c>
+      <c r="E23" t="n">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>595</v>
+      </c>
+      <c r="D24" t="n">
+        <v>88</v>
+      </c>
+      <c r="E24" t="n">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>0</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>565</v>
+      </c>
+      <c r="D25" t="n">
+        <v>311</v>
+      </c>
+      <c r="E25" t="n">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>0</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>928</v>
+      </c>
+      <c r="D26" t="n">
+        <v>32</v>
+      </c>
+      <c r="E26" t="n">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>0</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>806</v>
+      </c>
+      <c r="D27" t="n">
+        <v>162</v>
+      </c>
+      <c r="E27" t="n">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>0</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>462</v>
+      </c>
+      <c r="D28" t="n">
+        <v>70</v>
+      </c>
+      <c r="E28" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>0</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>450</v>
+      </c>
+      <c r="D29" t="n">
+        <v>292</v>
+      </c>
+      <c r="E29" t="n">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>0</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>765</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>649</v>
+      </c>
+      <c r="D31" t="n">
+        <v>339</v>
+      </c>
+      <c r="E31" t="n">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>737</v>
+      </c>
+      <c r="D32" t="n">
+        <v>74</v>
+      </c>
+      <c r="E32" t="n">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>0</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>730</v>
+      </c>
+      <c r="D33" t="n">
+        <v>139</v>
+      </c>
+      <c r="E33" t="n">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>751</v>
+      </c>
+      <c r="D34" t="n">
+        <v>481</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D35" t="n">
+        <v>32</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1148</v>
+      </c>
+      <c r="D36" t="n">
+        <v>273</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>711</v>
+      </c>
+      <c r="D37" t="n">
+        <v>105</v>
+      </c>
+      <c r="E37" t="n">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>735</v>
+      </c>
+      <c r="D38" t="n">
+        <v>147</v>
+      </c>
+      <c r="E38" t="n">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>756</v>
+      </c>
+      <c r="D39" t="n">
+        <v>277</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D40" t="n">
+        <v>27</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>981</v>
+      </c>
+      <c r="D41" t="n">
+        <v>228</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>635</v>
+      </c>
+      <c r="D42" t="n">
+        <v>101</v>
+      </c>
+      <c r="E42" t="n">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>0</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>655</v>
+      </c>
+      <c r="D43" t="n">
+        <v>73</v>
+      </c>
+      <c r="E43" t="n">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>0</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>707</v>
+      </c>
+      <c r="D44" t="n">
+        <v>63</v>
+      </c>
+      <c r="E44" t="n">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>0</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>707</v>
+      </c>
+      <c r="D45" t="n">
+        <v>70</v>
+      </c>
+      <c r="E45" t="n">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>0</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>659</v>
+      </c>
+      <c r="D46" t="n">
+        <v>539</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>0</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>0</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1175</v>
+      </c>
+      <c r="D48" t="n">
+        <v>160</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>0</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>575</v>
+      </c>
+      <c r="D49" t="n">
+        <v>74</v>
+      </c>
+      <c r="E49" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>568</v>
+      </c>
+      <c r="D50" t="n">
+        <v>86</v>
+      </c>
+      <c r="E50" t="n">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>0</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>536</v>
+      </c>
+      <c r="D51" t="n">
+        <v>374</v>
+      </c>
+      <c r="E51" t="n">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>942</v>
+      </c>
+      <c r="D52" t="n">
+        <v>47</v>
+      </c>
+      <c r="E52" t="n">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>0</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>840</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>0</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D54" t="n">
+        <v>59</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>0</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D55" t="n">
+        <v>345</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>0</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1229</v>
+      </c>
+      <c r="D56" t="n">
+        <v>315</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1544</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>0</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1614</v>
+      </c>
+      <c r="D57" t="n">
+        <v>32</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>0</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1492</v>
+      </c>
+      <c r="D58" t="n">
+        <v>388</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>0</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>798</v>
+      </c>
+      <c r="D59" t="n">
+        <v>77</v>
+      </c>
+      <c r="E59" t="n">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>0</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>794</v>
+      </c>
+      <c r="D60" t="n">
+        <v>225</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>0</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>901</v>
+      </c>
+      <c r="D61" t="n">
+        <v>427</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>0</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1378</v>
+      </c>
+      <c r="D62" t="n">
+        <v>32</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>0</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1256</v>
+      </c>
+      <c r="D63" t="n">
+        <v>305</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>0</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>644</v>
+      </c>
+      <c r="D64" t="n">
+        <v>73</v>
+      </c>
+      <c r="E64" t="n">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>0</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>636</v>
+      </c>
+      <c r="D65" t="n">
+        <v>90</v>
+      </c>
+      <c r="E65" t="n">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>0</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>608</v>
+      </c>
+      <c r="D66" t="n">
+        <v>362</v>
+      </c>
+      <c r="E66" t="n">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>0</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D67" t="n">
+        <v>101</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>0</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1085</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>0</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>999</v>
+      </c>
+      <c r="D69" t="n">
+        <v>126</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>0</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>676</v>
+      </c>
+      <c r="D70" t="n">
+        <v>59</v>
+      </c>
+      <c r="E70" t="n">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>0</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>654</v>
+      </c>
+      <c r="D71" t="n">
+        <v>144</v>
+      </c>
+      <c r="E71" t="n">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>0</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>680</v>
+      </c>
+      <c r="D72" t="n">
+        <v>517</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>0</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>614</v>
+      </c>
+      <c r="D73" t="n">
+        <v>98</v>
+      </c>
+      <c r="E73" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>0</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>631</v>
+      </c>
+      <c r="D74" t="n">
+        <v>103</v>
+      </c>
+      <c r="E74" t="n">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>0</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>616</v>
+      </c>
+      <c r="D75" t="n">
+        <v>315</v>
+      </c>
+      <c r="E75" t="n">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>0</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>983</v>
+      </c>
+      <c r="D76" t="n">
+        <v>27</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>0</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>861</v>
+      </c>
+      <c r="D77" t="n">
+        <v>147</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>0</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>848</v>
+      </c>
+      <c r="D78" t="n">
+        <v>75</v>
+      </c>
+      <c r="E78" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>0</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>842</v>
+      </c>
+      <c r="D79" t="n">
+        <v>212</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>0</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>936</v>
+      </c>
+      <c r="D80" t="n">
+        <v>458</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>0</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1447</v>
+      </c>
+      <c r="D81" t="n">
+        <v>32</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>0</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1325</v>
+      </c>
+      <c r="D82" t="n">
+        <v>398</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>0</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>607</v>
+      </c>
+      <c r="D83" t="n">
+        <v>108</v>
+      </c>
+      <c r="E83" t="n">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>0</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>634</v>
+      </c>
+      <c r="D84" t="n">
+        <v>88</v>
+      </c>
+      <c r="E84" t="n">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>0</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>604</v>
+      </c>
+      <c r="D85" t="n">
+        <v>341</v>
+      </c>
+      <c r="E85" t="n">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>0</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D86" t="n">
+        <v>27</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>0</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>893</v>
+      </c>
+      <c r="D87" t="n">
+        <v>149</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>0</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>462</v>
+      </c>
+      <c r="D88" t="n">
+        <v>79</v>
+      </c>
+      <c r="E88" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>0</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>460</v>
+      </c>
+      <c r="D89" t="n">
+        <v>259</v>
+      </c>
+      <c r="E89" t="n">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>0</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>601</v>
+      </c>
+      <c r="D90" t="n">
+        <v>283</v>
+      </c>
+      <c r="E90" t="n">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>0</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>936</v>
+      </c>
+      <c r="D91" t="n">
+        <v>27</v>
+      </c>
+      <c r="E91" t="n">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>0</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>814</v>
+      </c>
+      <c r="D92" t="n">
+        <v>297</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>0</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>737</v>
+      </c>
+      <c r="D93" t="n">
+        <v>74</v>
+      </c>
+      <c r="E93" t="n">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>0</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>730</v>
+      </c>
+      <c r="D94" t="n">
+        <v>139</v>
+      </c>
+      <c r="E94" t="n">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>0</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>751</v>
+      </c>
+      <c r="D95" t="n">
+        <v>491</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>0</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1276</v>
+      </c>
+      <c r="D96" t="n">
+        <v>32</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>0</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1154</v>
+      </c>
+      <c r="D97" t="n">
+        <v>270</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>0</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>711</v>
+      </c>
+      <c r="D98" t="n">
+        <v>105</v>
+      </c>
+      <c r="E98" t="n">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>0</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>734</v>
+      </c>
+      <c r="D99" t="n">
+        <v>148</v>
+      </c>
+      <c r="E99" t="n">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>0</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>905</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>0</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>789</v>
+      </c>
+      <c r="D101" t="n">
+        <v>222</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>0</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>635</v>
+      </c>
+      <c r="D102" t="n">
+        <v>101</v>
+      </c>
+      <c r="E102" t="n">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>0</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>655</v>
+      </c>
+      <c r="D103" t="n">
+        <v>73</v>
+      </c>
+      <c r="E103" t="n">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>0</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>707</v>
+      </c>
+      <c r="D104" t="n">
+        <v>63</v>
+      </c>
+      <c r="E104" t="n">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>0</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>707</v>
+      </c>
+      <c r="D105" t="n">
+        <v>70</v>
+      </c>
+      <c r="E105" t="n">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>0</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>659</v>
+      </c>
+      <c r="D106" t="n">
+        <v>314</v>
+      </c>
+      <c r="E106" t="n">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>0</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>0</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>949</v>
+      </c>
+      <c r="D108" t="n">
+        <v>102</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>0</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>575</v>
+      </c>
+      <c r="D109" t="n">
+        <v>73</v>
+      </c>
+      <c r="E109" t="n">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>0</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>567</v>
+      </c>
+      <c r="D110" t="n">
+        <v>87</v>
+      </c>
+      <c r="E110" t="n">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>0</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>534</v>
+      </c>
+      <c r="D111" t="n">
+        <v>383</v>
+      </c>
+      <c r="E111" t="n">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>0</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>944</v>
+      </c>
+      <c r="D112" t="n">
+        <v>32</v>
+      </c>
+      <c r="E112" t="n">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>0</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>822</v>
+      </c>
+      <c r="D113" t="n">
+        <v>40</v>
+      </c>
+      <c r="E113" t="n">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>0</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D114" t="n">
+        <v>62</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>0</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D115" t="n">
+        <v>220</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>0</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1133</v>
+      </c>
+      <c r="D116" t="n">
+        <v>354</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>0</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>1539</v>
+      </c>
+      <c r="D117" t="n">
+        <v>50</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>0</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>1526</v>
+      </c>
+      <c r="D118" t="n">
         <v>205</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E118" t="n">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>0</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1754</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>0</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>1638</v>
+      </c>
+      <c r="D120" t="n">
+        <v>378</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>0</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>614</v>
+      </c>
+      <c r="D121" t="n">
+        <v>98</v>
+      </c>
+      <c r="E121" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>0</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>631</v>
+      </c>
+      <c r="D122" t="n">
+        <v>103</v>
+      </c>
+      <c r="E122" t="n">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>0</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>616</v>
+      </c>
+      <c r="D123" t="n">
+        <v>345</v>
+      </c>
+      <c r="E123" t="n">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>0</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D124" t="n">
+        <v>58</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>0</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D125" t="n">
+        <v>85</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>0</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1121</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>0</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D127" t="n">
+        <v>168</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>1</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>848</v>
+      </c>
+      <c r="D128" t="n">
+        <v>75</v>
+      </c>
+      <c r="E128" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>842</v>
+      </c>
+      <c r="D129" t="n">
+        <v>189</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>1</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>913</v>
+      </c>
+      <c r="D130" t="n">
+        <v>373</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>1</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1338</v>
+      </c>
+      <c r="D131" t="n">
+        <v>54</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>1</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1329</v>
+      </c>
+      <c r="D132" t="n">
+        <v>173</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>1</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D133" t="n">
+        <v>54</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1554</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>1</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D134" t="n">
+        <v>173</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>1</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1538</v>
+      </c>
+      <c r="D135" t="n">
+        <v>324</v>
+      </c>
+      <c r="E135" t="n">
         <v>1862</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>2</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>607</v>
+      </c>
+      <c r="D136" t="n">
+        <v>69</v>
+      </c>
+      <c r="E136" t="n">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>2</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>595</v>
+      </c>
+      <c r="D137" t="n">
+        <v>88</v>
+      </c>
+      <c r="E137" t="n">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>2</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>565</v>
+      </c>
+      <c r="D138" t="n">
+        <v>302</v>
+      </c>
+      <c r="E138" t="n">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>2</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>919</v>
+      </c>
+      <c r="D139" t="n">
+        <v>40</v>
+      </c>
+      <c r="E139" t="n">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>2</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>901</v>
+      </c>
+      <c r="D140" t="n">
+        <v>73</v>
+      </c>
+      <c r="E140" t="n">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>2</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>997</v>
+      </c>
+      <c r="D141" t="n">
+        <v>3</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>2</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>881</v>
+      </c>
+      <c r="D142" t="n">
+        <v>165</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>3</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>462</v>
+      </c>
+      <c r="D143" t="n">
+        <v>79</v>
+      </c>
+      <c r="E143" t="n">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>3</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>460</v>
+      </c>
+      <c r="D144" t="n">
+        <v>259</v>
+      </c>
+      <c r="E144" t="n">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>3</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>601</v>
+      </c>
+      <c r="D145" t="n">
+        <v>298</v>
+      </c>
+      <c r="E145" t="n">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>3</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>951</v>
+      </c>
+      <c r="D146" t="n">
+        <v>49</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>3</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>937</v>
+      </c>
+      <c r="D147" t="n">
+        <v>244</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>3</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1204</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>3</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>1088</v>
+      </c>
+      <c r="D149" t="n">
+        <v>314</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>4</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>737</v>
+      </c>
+      <c r="D150" t="n">
+        <v>74</v>
+      </c>
+      <c r="E150" t="n">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>4</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>730</v>
+      </c>
+      <c r="D151" t="n">
+        <v>139</v>
+      </c>
+      <c r="E151" t="n">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>4</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>751</v>
+      </c>
+      <c r="D152" t="n">
+        <v>492</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>4</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>1278</v>
+      </c>
+      <c r="D153" t="n">
+        <v>45</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>4</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>1285</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>4</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D155" t="n">
+        <v>223</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>5</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>711</v>
+      </c>
+      <c r="D156" t="n">
+        <v>105</v>
+      </c>
+      <c r="E156" t="n">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>5</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>734</v>
+      </c>
+      <c r="D157" t="n">
+        <v>143</v>
+      </c>
+      <c r="E157" t="n">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>5</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>900</v>
+      </c>
+      <c r="D158" t="n">
+        <v>3</v>
+      </c>
+      <c r="E158" t="n">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>5</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>784</v>
+      </c>
+      <c r="D159" t="n">
+        <v>214</v>
+      </c>
+      <c r="E159" t="n">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>6</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>635</v>
+      </c>
+      <c r="D160" t="n">
+        <v>101</v>
+      </c>
+      <c r="E160" t="n">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>6</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>655</v>
+      </c>
+      <c r="D161" t="n">
+        <v>73</v>
+      </c>
+      <c r="E161" t="n">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>6</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>707</v>
+      </c>
+      <c r="D162" t="n">
+        <v>63</v>
+      </c>
+      <c r="E162" t="n">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>6</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>707</v>
+      </c>
+      <c r="D163" t="n">
+        <v>70</v>
+      </c>
+      <c r="E163" t="n">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>6</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>659</v>
+      </c>
+      <c r="D164" t="n">
+        <v>345</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>6</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>1096</v>
+      </c>
+      <c r="D165" t="n">
+        <v>27</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>6</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>974</v>
+      </c>
+      <c r="D166" t="n">
+        <v>125</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>7</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>575</v>
+      </c>
+      <c r="D167" t="n">
+        <v>73</v>
+      </c>
+      <c r="E167" t="n">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>7</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>567</v>
+      </c>
+      <c r="D168" t="n">
+        <v>87</v>
+      </c>
+      <c r="E168" t="n">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>7</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>534</v>
+      </c>
+      <c r="D169" t="n">
+        <v>424</v>
+      </c>
+      <c r="E169" t="n">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>7</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>987</v>
+      </c>
+      <c r="D170" t="n">
+        <v>117</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>7</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1071</v>
+      </c>
+      <c r="D171" t="n">
+        <v>3</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>7</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>985</v>
+      </c>
+      <c r="D172" t="n">
+        <v>159</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>8</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D173" t="n">
+        <v>59</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>8</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D174" t="n">
+        <v>345</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>8</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1229</v>
+      </c>
+      <c r="D175" t="n">
+        <v>316</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>8</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>1615</v>
+      </c>
+      <c r="D176" t="n">
+        <v>50</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>8</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>1602</v>
+      </c>
+      <c r="D177" t="n">
+        <v>327</v>
+      </c>
+      <c r="E177" t="n">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>8</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D178" t="n">
+        <v>3</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>8</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1836</v>
+      </c>
+      <c r="D179" t="n">
+        <v>382</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>9</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>832</v>
+      </c>
+      <c r="D180" t="n">
+        <v>63</v>
+      </c>
+      <c r="E180" t="n">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>9</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>814</v>
+      </c>
+      <c r="D181" t="n">
+        <v>300</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>9</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>996</v>
+      </c>
+      <c r="D182" t="n">
+        <v>408</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>9</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>1457</v>
+      </c>
+      <c r="D183" t="n">
+        <v>65</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>9</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1368</v>
+      </c>
+      <c r="D184" t="n">
+        <v>3</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>10</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>550</v>
+      </c>
+      <c r="D185" t="n">
+        <v>62</v>
+      </c>
+      <c r="E185" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>10</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>531</v>
+      </c>
+      <c r="D186" t="n">
+        <v>79</v>
+      </c>
+      <c r="E186" t="n">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>10</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>492</v>
+      </c>
+      <c r="D187" t="n">
+        <v>334</v>
+      </c>
+      <c r="E187" t="n">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>10</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>878</v>
+      </c>
+      <c r="D188" t="n">
+        <v>66</v>
+      </c>
+      <c r="E188" t="n">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>10</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>881</v>
+      </c>
+      <c r="D189" t="n">
+        <v>60</v>
+      </c>
+      <c r="E189" t="n">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>10</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>842</v>
+      </c>
+      <c r="D190" t="n">
+        <v>224</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>10</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>1136</v>
+      </c>
+      <c r="D191" t="n">
+        <v>63</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>10</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1045</v>
+      </c>
+      <c r="D192" t="n">
+        <v>154</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>11</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>730</v>
+      </c>
+      <c r="D193" t="n">
+        <v>80</v>
+      </c>
+      <c r="E193" t="n">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>11</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>729</v>
+      </c>
+      <c r="D194" t="n">
+        <v>145</v>
+      </c>
+      <c r="E194" t="n">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>11</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>756</v>
+      </c>
+      <c r="D195" t="n">
+        <v>367</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>11</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>1175</v>
+      </c>
+      <c r="D196" t="n">
+        <v>44</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>11</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D197" t="n">
+        <v>126</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>11</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>1188</v>
+      </c>
+      <c r="D198" t="n">
+        <v>266</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>11</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>1524</v>
+      </c>
+      <c r="D199" t="n">
+        <v>49</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>11</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>1510</v>
+      </c>
+      <c r="D200" t="n">
+        <v>126</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>11</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1537</v>
+      </c>
+      <c r="D201" t="n">
+        <v>502</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>11</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D202" t="n">
+        <v>362</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>12</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>585</v>
+      </c>
+      <c r="D203" t="n">
+        <v>70</v>
+      </c>
+      <c r="E203" t="n">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>12</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>574</v>
+      </c>
+      <c r="D204" t="n">
+        <v>70</v>
+      </c>
+      <c r="E204" t="n">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>12</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>526</v>
+      </c>
+      <c r="D205" t="n">
+        <v>276</v>
+      </c>
+      <c r="E205" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>12</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>854</v>
+      </c>
+      <c r="D206" t="n">
+        <v>27</v>
+      </c>
+      <c r="E206" t="n">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>12</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>732</v>
+      </c>
+      <c r="D207" t="n">
+        <v>126</v>
+      </c>
+      <c r="E207" t="n">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>13</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>835</v>
+      </c>
+      <c r="D208" t="n">
+        <v>58</v>
+      </c>
+      <c r="E208" t="n">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>13</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>812</v>
+      </c>
+      <c r="D209" t="n">
+        <v>233</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>13</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>910</v>
+      </c>
+      <c r="D210" t="n">
+        <v>425</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>13</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1379</v>
+      </c>
+      <c r="D211" t="n">
+        <v>57</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1436</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>13</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>1373</v>
+      </c>
+      <c r="D212" t="n">
+        <v>3</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>13</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1287</v>
+      </c>
+      <c r="D213" t="n">
+        <v>258</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>14</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>583</v>
+      </c>
+      <c r="D214" t="n">
+        <v>69</v>
+      </c>
+      <c r="E214" t="n">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>14</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>570</v>
+      </c>
+      <c r="D215" t="n">
+        <v>83</v>
+      </c>
+      <c r="E215" t="n">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>14</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>676</v>
+      </c>
+      <c r="D216" t="n">
+        <v>3</v>
+      </c>
+      <c r="E216" t="n">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>14</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>560</v>
+      </c>
+      <c r="D217" t="n">
+        <v>134</v>
+      </c>
+      <c r="E217" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>15</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>714</v>
+      </c>
+      <c r="D218" t="n">
+        <v>59</v>
+      </c>
+      <c r="E218" t="n">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>15</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>692</v>
+      </c>
+      <c r="D219" t="n">
+        <v>143</v>
+      </c>
+      <c r="E219" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>15</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>717</v>
+      </c>
+      <c r="D220" t="n">
+        <v>267</v>
+      </c>
+      <c r="E220" t="n">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>15</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D221" t="n">
+        <v>48</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>15</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D222" t="n">
+        <v>125</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>15</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>1169</v>
+      </c>
+      <c r="D223" t="n">
+        <v>3</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>15</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D224" t="n">
+        <v>251</v>
+      </c>
+      <c r="E224" t="n">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>16</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>822</v>
+      </c>
+      <c r="D225" t="n">
+        <v>65</v>
+      </c>
+      <c r="E225" t="n">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>16</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>806</v>
+      </c>
+      <c r="D226" t="n">
+        <v>212</v>
+      </c>
+      <c r="E226" t="n">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>16</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>900</v>
+      </c>
+      <c r="D227" t="n">
+        <v>353</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>16</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>1305</v>
+      </c>
+      <c r="D228" t="n">
+        <v>50</v>
+      </c>
+      <c r="E228" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>16</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>1292</v>
+      </c>
+      <c r="D229" t="n">
+        <v>194</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>16</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1509</v>
+      </c>
+      <c r="D230" t="n">
+        <v>3</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1512</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>16</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1393</v>
+      </c>
+      <c r="D231" t="n">
+        <v>250</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>17</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1232</v>
+      </c>
+      <c r="D232" t="n">
+        <v>68</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>17</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1219</v>
+      </c>
+      <c r="D233" t="n">
+        <v>479</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>17</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D234" t="n">
+        <v>451</v>
+      </c>
+      <c r="E234" t="n">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>17</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>2123</v>
+      </c>
+      <c r="D235" t="n">
+        <v>3</v>
+      </c>
+      <c r="E235" t="n">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>17</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>2007</v>
+      </c>
+      <c r="D236" t="n">
+        <v>553</v>
+      </c>
+      <c r="E236" t="n">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>18</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>563</v>
+      </c>
+      <c r="D237" t="n">
+        <v>111</v>
+      </c>
+      <c r="E237" t="n">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>18</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>593</v>
+      </c>
+      <c r="D238" t="n">
+        <v>73</v>
+      </c>
+      <c r="E238" t="n">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>18</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>645</v>
+      </c>
+      <c r="D239" t="n">
+        <v>76</v>
+      </c>
+      <c r="E239" t="n">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>18</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>658</v>
+      </c>
+      <c r="D240" t="n">
+        <v>54</v>
+      </c>
+      <c r="E240" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>18</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>710</v>
+      </c>
+      <c r="D241" t="n">
+        <v>74</v>
+      </c>
+      <c r="E241" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>18</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>721</v>
+      </c>
+      <c r="D242" t="n">
+        <v>73</v>
+      </c>
+      <c r="E242" t="n">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>18</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>692</v>
+      </c>
+      <c r="D243" t="n">
+        <v>107</v>
+      </c>
+      <c r="E243" t="n">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>19</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>894</v>
+      </c>
+      <c r="D244" t="n">
+        <v>64</v>
+      </c>
+      <c r="E244" t="n">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>19</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>877</v>
+      </c>
+      <c r="D245" t="n">
+        <v>246</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>19</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D246" t="n">
+        <v>345</v>
+      </c>
+      <c r="E246" t="n">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>19</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>1420</v>
+      </c>
+      <c r="D247" t="n">
+        <v>49</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>19</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>1406</v>
+      </c>
+      <c r="D248" t="n">
+        <v>227</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>19</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>1534</v>
+      </c>
+      <c r="D249" t="n">
+        <v>250</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>19</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1854</v>
+      </c>
+      <c r="D250" t="n">
+        <v>49</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>19</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>1840</v>
+      </c>
+      <c r="D251" t="n">
+        <v>230</v>
+      </c>
+      <c r="E251" t="n">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>19</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>1944</v>
+      </c>
+      <c r="D252" t="n">
+        <v>433</v>
+      </c>
+      <c r="E252" t="n">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>0</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>614</v>
+      </c>
+      <c r="D253" t="n">
+        <v>98</v>
+      </c>
+      <c r="E253" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>0</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>631</v>
+      </c>
+      <c r="D254" t="n">
+        <v>103</v>
+      </c>
+      <c r="E254" t="n">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>0</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>616</v>
+      </c>
+      <c r="D255" t="n">
+        <v>334</v>
+      </c>
+      <c r="E255" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>0</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D256" t="n">
+        <v>50</v>
+      </c>
+      <c r="E256" t="n">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>0</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>994</v>
+      </c>
+      <c r="D257" t="n">
+        <v>85</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>0</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>1102</v>
+      </c>
+      <c r="D258" t="n">
+        <v>3</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>0</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>986</v>
+      </c>
+      <c r="D259" t="n">
+        <v>130</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>1</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>848</v>
+      </c>
+      <c r="D260" t="n">
+        <v>75</v>
+      </c>
+      <c r="E260" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>1</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>842</v>
+      </c>
+      <c r="D261" t="n">
+        <v>189</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>1</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>913</v>
+      </c>
+      <c r="D262" t="n">
+        <v>362</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>1</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>1327</v>
+      </c>
+      <c r="D263" t="n">
+        <v>49</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1376</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>1</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>1313</v>
+      </c>
+      <c r="D264" t="n">
+        <v>174</v>
+      </c>
+      <c r="E264" t="n">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>1</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>1510</v>
+      </c>
+      <c r="D265" t="n">
+        <v>3</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1513</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>1</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>1394</v>
+      </c>
+      <c r="D266" t="n">
+        <v>301</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>2</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>607</v>
+      </c>
+      <c r="D267" t="n">
+        <v>108</v>
+      </c>
+      <c r="E267" t="n">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>2</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>634</v>
+      </c>
+      <c r="D268" t="n">
+        <v>88</v>
+      </c>
+      <c r="E268" t="n">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>2</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>604</v>
+      </c>
+      <c r="D269" t="n">
+        <v>332</v>
+      </c>
+      <c r="E269" t="n">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>2</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D270" t="n">
+        <v>27</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>2</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>884</v>
+      </c>
+      <c r="D271" t="n">
+        <v>146</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>3</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>462</v>
+      </c>
+      <c r="D272" t="n">
+        <v>70</v>
+      </c>
+      <c r="E272" t="n">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>3</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>450</v>
+      </c>
+      <c r="D273" t="n">
+        <v>296</v>
+      </c>
+      <c r="E273" t="n">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>3</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>769</v>
+      </c>
+      <c r="D274" t="n">
+        <v>3</v>
+      </c>
+      <c r="E274" t="n">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>3</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>653</v>
+      </c>
+      <c r="D275" t="n">
+        <v>362</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>4</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>737</v>
+      </c>
+      <c r="D276" t="n">
+        <v>74</v>
+      </c>
+      <c r="E276" t="n">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>4</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>730</v>
+      </c>
+      <c r="D277" t="n">
+        <v>139</v>
+      </c>
+      <c r="E277" t="n">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>4</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>751</v>
+      </c>
+      <c r="D278" t="n">
+        <v>492</v>
+      </c>
+      <c r="E278" t="n">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>4</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>1278</v>
+      </c>
+      <c r="D279" t="n">
+        <v>45</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>4</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>1285</v>
+      </c>
+      <c r="D280" t="n">
+        <v>3</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>4</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D281" t="n">
+        <v>208</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>5</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>711</v>
+      </c>
+      <c r="D282" t="n">
+        <v>105</v>
+      </c>
+      <c r="E282" t="n">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>5</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>734</v>
+      </c>
+      <c r="D283" t="n">
+        <v>148</v>
+      </c>
+      <c r="E283" t="n">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>5</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>905</v>
+      </c>
+      <c r="D284" t="n">
+        <v>3</v>
+      </c>
+      <c r="E284" t="n">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>5</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>789</v>
+      </c>
+      <c r="D285" t="n">
+        <v>223</v>
+      </c>
+      <c r="E285" t="n">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>6</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>635</v>
+      </c>
+      <c r="D286" t="n">
+        <v>101</v>
+      </c>
+      <c r="E286" t="n">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>6</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>655</v>
+      </c>
+      <c r="D287" t="n">
+        <v>73</v>
+      </c>
+      <c r="E287" t="n">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>6</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>707</v>
+      </c>
+      <c r="D288" t="n">
+        <v>63</v>
+      </c>
+      <c r="E288" t="n">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>6</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>707</v>
+      </c>
+      <c r="D289" t="n">
+        <v>70</v>
+      </c>
+      <c r="E289" t="n">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>6</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>659</v>
+      </c>
+      <c r="D290" t="n">
+        <v>289</v>
+      </c>
+      <c r="E290" t="n">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>6</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D291" t="n">
+        <v>27</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>6</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>918</v>
+      </c>
+      <c r="D292" t="n">
+        <v>186</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>7</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>575</v>
+      </c>
+      <c r="D293" t="n">
+        <v>73</v>
+      </c>
+      <c r="E293" t="n">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>7</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>567</v>
+      </c>
+      <c r="D294" t="n">
+        <v>87</v>
+      </c>
+      <c r="E294" t="n">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>7</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>534</v>
+      </c>
+      <c r="D295" t="n">
+        <v>335</v>
+      </c>
+      <c r="E295" t="n">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>7</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>921</v>
+      </c>
+      <c r="D296" t="n">
+        <v>32</v>
+      </c>
+      <c r="E296" t="n">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>7</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>799</v>
+      </c>
+      <c r="D297" t="n">
+        <v>143</v>
+      </c>
+      <c r="E297" t="n">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>8</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D298" t="n">
+        <v>59</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>8</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D299" t="n">
+        <v>345</v>
+      </c>
+      <c r="E299" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>8</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>1229</v>
+      </c>
+      <c r="D300" t="n">
+        <v>304</v>
+      </c>
+      <c r="E300" t="n">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>8</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>1603</v>
+      </c>
+      <c r="D301" t="n">
+        <v>48</v>
+      </c>
+      <c r="E301" t="n">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>8</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>1588</v>
+      </c>
+      <c r="D302" t="n">
+        <v>327</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>8</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>1938</v>
+      </c>
+      <c r="D303" t="n">
+        <v>3</v>
+      </c>
+      <c r="E303" t="n">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>8</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>1822</v>
+      </c>
+      <c r="D304" t="n">
+        <v>422</v>
+      </c>
+      <c r="E304" t="n">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>9</v>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>832</v>
+      </c>
+      <c r="D305" t="n">
+        <v>63</v>
+      </c>
+      <c r="E305" t="n">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>9</v>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>814</v>
+      </c>
+      <c r="D306" t="n">
+        <v>300</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>9</v>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>996</v>
+      </c>
+      <c r="D307" t="n">
+        <v>411</v>
+      </c>
+      <c r="E307" t="n">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>9</v>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>1458</v>
+      </c>
+      <c r="D308" t="n">
+        <v>68</v>
+      </c>
+      <c r="E308" t="n">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>9</v>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>1372</v>
+      </c>
+      <c r="D309" t="n">
+        <v>3</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>10</v>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>550</v>
+      </c>
+      <c r="D310" t="n">
+        <v>99</v>
+      </c>
+      <c r="E310" t="n">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>10</v>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>568</v>
+      </c>
+      <c r="D311" t="n">
+        <v>79</v>
+      </c>
+      <c r="E311" t="n">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>10</v>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>529</v>
+      </c>
+      <c r="D312" t="n">
+        <v>303</v>
+      </c>
+      <c r="E312" t="n">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>10</v>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>884</v>
+      </c>
+      <c r="D313" t="n">
+        <v>48</v>
+      </c>
+      <c r="E313" t="n">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>10</v>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>869</v>
+      </c>
+      <c r="D314" t="n">
+        <v>64</v>
+      </c>
+      <c r="E314" t="n">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>10</v>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>956</v>
+      </c>
+      <c r="D315" t="n">
+        <v>3</v>
+      </c>
+      <c r="E315" t="n">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>10</v>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>840</v>
+      </c>
+      <c r="D316" t="n">
+        <v>137</v>
+      </c>
+      <c r="E316" t="n">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>11</v>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>730</v>
+      </c>
+      <c r="D317" t="n">
+        <v>72</v>
+      </c>
+      <c r="E317" t="n">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>11</v>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>721</v>
+      </c>
+      <c r="D318" t="n">
+        <v>171</v>
+      </c>
+      <c r="E318" t="n">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>11</v>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>774</v>
+      </c>
+      <c r="D319" t="n">
+        <v>349</v>
+      </c>
+      <c r="E319" t="n">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>11</v>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>1175</v>
+      </c>
+      <c r="D320" t="n">
+        <v>27</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>11</v>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D321" t="n">
+        <v>326</v>
+      </c>
+      <c r="E321" t="n">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>12</v>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>585</v>
+      </c>
+      <c r="D322" t="n">
+        <v>70</v>
+      </c>
+      <c r="E322" t="n">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>12</v>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>574</v>
+      </c>
+      <c r="D323" t="n">
+        <v>70</v>
+      </c>
+      <c r="E323" t="n">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>12</v>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>526</v>
+      </c>
+      <c r="D324" t="n">
+        <v>290</v>
+      </c>
+      <c r="E324" t="n">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>12</v>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>868</v>
+      </c>
+      <c r="D325" t="n">
+        <v>45</v>
+      </c>
+      <c r="E325" t="n">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>12</v>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>855</v>
+      </c>
+      <c r="D326" t="n">
+        <v>52</v>
+      </c>
+      <c r="E326" t="n">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>12</v>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>930</v>
+      </c>
+      <c r="D327" t="n">
+        <v>3</v>
+      </c>
+      <c r="E327" t="n">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>12</v>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>814</v>
+      </c>
+      <c r="D328" t="n">
+        <v>105</v>
+      </c>
+      <c r="E328" t="n">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>13</v>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>835</v>
+      </c>
+      <c r="D329" t="n">
+        <v>58</v>
+      </c>
+      <c r="E329" t="n">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>13</v>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>812</v>
+      </c>
+      <c r="D330" t="n">
+        <v>233</v>
+      </c>
+      <c r="E330" t="n">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>13</v>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>910</v>
+      </c>
+      <c r="D331" t="n">
+        <v>408</v>
+      </c>
+      <c r="E331" t="n">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>13</v>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>1356</v>
+      </c>
+      <c r="D332" t="n">
+        <v>63</v>
+      </c>
+      <c r="E332" t="n">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>13</v>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>1265</v>
+      </c>
+      <c r="D333" t="n">
+        <v>303</v>
+      </c>
+      <c r="E333" t="n">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>14</v>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>583</v>
+      </c>
+      <c r="D334" t="n">
+        <v>69</v>
+      </c>
+      <c r="E334" t="n">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>14</v>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>570</v>
+      </c>
+      <c r="D335" t="n">
+        <v>83</v>
+      </c>
+      <c r="E335" t="n">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>14</v>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>676</v>
+      </c>
+      <c r="D336" t="n">
+        <v>3</v>
+      </c>
+      <c r="E336" t="n">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>14</v>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>560</v>
+      </c>
+      <c r="D337" t="n">
+        <v>141</v>
+      </c>
+      <c r="E337" t="n">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>15</v>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>714</v>
+      </c>
+      <c r="D338" t="n">
+        <v>59</v>
+      </c>
+      <c r="E338" t="n">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>15</v>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>692</v>
+      </c>
+      <c r="D339" t="n">
+        <v>143</v>
+      </c>
+      <c r="E339" t="n">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>15</v>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>717</v>
+      </c>
+      <c r="D340" t="n">
+        <v>333</v>
+      </c>
+      <c r="E340" t="n">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>15</v>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>1102</v>
+      </c>
+      <c r="D341" t="n">
+        <v>27</v>
+      </c>
+      <c r="E341" t="n">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>15</v>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>980</v>
+      </c>
+      <c r="D342" t="n">
+        <v>237</v>
+      </c>
+      <c r="E342" t="n">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>16</v>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>822</v>
+      </c>
+      <c r="D343" t="n">
+        <v>65</v>
+      </c>
+      <c r="E343" t="n">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>16</v>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>806</v>
+      </c>
+      <c r="D344" t="n">
+        <v>212</v>
+      </c>
+      <c r="E344" t="n">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>16</v>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>900</v>
+      </c>
+      <c r="D345" t="n">
+        <v>305</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>16</v>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>1257</v>
+      </c>
+      <c r="D346" t="n">
+        <v>51</v>
+      </c>
+      <c r="E346" t="n">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>16</v>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>1135</v>
+      </c>
+      <c r="D347" t="n">
+        <v>381</v>
+      </c>
+      <c r="E347" t="n">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>17</v>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>1232</v>
+      </c>
+      <c r="D348" t="n">
+        <v>68</v>
+      </c>
+      <c r="E348" t="n">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>17</v>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>1219</v>
+      </c>
+      <c r="D349" t="n">
+        <v>479</v>
+      </c>
+      <c r="E349" t="n">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>17</v>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D350" t="n">
+        <v>504</v>
+      </c>
+      <c r="E350" t="n">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>17</v>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>2124</v>
+      </c>
+      <c r="D351" t="n">
+        <v>32</v>
+      </c>
+      <c r="E351" t="n">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>17</v>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D352" t="n">
+        <v>809</v>
+      </c>
+      <c r="E352" t="n">
+        <v>2811</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>18</v>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>563</v>
+      </c>
+      <c r="D353" t="n">
+        <v>111</v>
+      </c>
+      <c r="E353" t="n">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>18</v>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>593</v>
+      </c>
+      <c r="D354" t="n">
+        <v>73</v>
+      </c>
+      <c r="E354" t="n">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>18</v>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>645</v>
+      </c>
+      <c r="D355" t="n">
+        <v>76</v>
+      </c>
+      <c r="E355" t="n">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>18</v>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>658</v>
+      </c>
+      <c r="D356" t="n">
+        <v>54</v>
+      </c>
+      <c r="E356" t="n">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>18</v>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>710</v>
+      </c>
+      <c r="D357" t="n">
+        <v>74</v>
+      </c>
+      <c r="E357" t="n">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>18</v>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>721</v>
+      </c>
+      <c r="D358" t="n">
+        <v>73</v>
+      </c>
+      <c r="E358" t="n">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>18</v>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>692</v>
+      </c>
+      <c r="D359" t="n">
+        <v>108</v>
+      </c>
+      <c r="E359" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>19</v>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>894</v>
+      </c>
+      <c r="D360" t="n">
+        <v>74</v>
+      </c>
+      <c r="E360" t="n">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>19</v>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>887</v>
+      </c>
+      <c r="D361" t="n">
+        <v>267</v>
+      </c>
+      <c r="E361" t="n">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>19</v>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>critic</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D362" t="n">
+        <v>493</v>
+      </c>
+      <c r="E362" t="n">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>19</v>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>1556</v>
+      </c>
+      <c r="D363" t="n">
+        <v>68</v>
+      </c>
+      <c r="E363" t="n">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>19</v>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>code_analyser</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>1542</v>
+      </c>
+      <c r="D364" t="n">
+        <v>249</v>
+      </c>
+      <c r="E364" t="n">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>19</v>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>supervisor</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>1814</v>
+      </c>
+      <c r="D365" t="n">
+        <v>3</v>
+      </c>
+      <c r="E365" t="n">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>19</v>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>finalizer</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>1698</v>
+      </c>
+      <c r="D366" t="n">
+        <v>398</v>
+      </c>
+      <c r="E366" t="n">
+        <v>2096</v>
       </c>
     </row>
   </sheetData>
